--- a/OUTPUT/gate_oof/fold_1/expert_inner_metrics.xlsx
+++ b/OUTPUT/gate_oof/fold_1/expert_inner_metrics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -535,10 +535,10 @@
         <v>460</v>
       </c>
       <c r="H2" t="n">
-        <v>2.243080099999133</v>
+        <v>2.00507519999519</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03625909999936994</v>
+        <v>0.01925149996532127</v>
       </c>
       <c r="J2" t="n">
         <v>0.003509784438385216</v>
@@ -587,31 +587,31 @@
         <v>752</v>
       </c>
       <c r="H3" t="n">
-        <v>6.067123999999239</v>
+        <v>3.798181399994064</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4737933000014891</v>
+        <v>0.4272457999759354</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005679055902877594</v>
+        <v>0.005638479650173871</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004086339889718967</v>
+        <v>0.004068624463148496</v>
       </c>
       <c r="L3" t="n">
-        <v>0.700306911158227</v>
+        <v>0.7045741627044165</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4255281228037743</v>
+        <v>0.423689490532645</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0003425428218989282</v>
+        <v>-0.0003331596223447861</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01192607385594081</v>
+        <v>0.01187034474042179</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02309238587491824</v>
+        <v>0.02262587604642641</v>
       </c>
     </row>
     <row r="4">
@@ -639,31 +639,31 @@
         <v>1442</v>
       </c>
       <c r="H4" t="n">
-        <v>10.96764950000033</v>
+        <v>34.44706429995131</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4209078000003501</v>
+        <v>0.3518164000124671</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005495652114654076</v>
+        <v>0.005494870526843252</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004183901178494823</v>
+        <v>0.004185088408052081</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5880720280016938</v>
+        <v>0.5881891878876628</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4241530982513992</v>
+        <v>0.4242743651389431</v>
       </c>
       <c r="N4" t="n">
-        <v>9.654593230333953e-05</v>
+        <v>9.861526700039952e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01138138520286331</v>
+        <v>0.01141165922443638</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02011945011123839</v>
+        <v>0.02051132436747438</v>
       </c>
     </row>
     <row r="5">
@@ -691,10 +691,10 @@
         <v>460</v>
       </c>
       <c r="H5" t="n">
-        <v>2.484147400000438</v>
+        <v>1.656787500018254</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02483850000135135</v>
+        <v>0.01950990001205355</v>
       </c>
       <c r="J5" t="n">
         <v>0.003489797672641565</v>
@@ -743,31 +743,31 @@
         <v>751</v>
       </c>
       <c r="H6" t="n">
-        <v>5.336233100000754</v>
+        <v>3.699478399998043</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4665325000005396</v>
+        <v>0.3874209999921732</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0054092481090178</v>
+        <v>0.005424600551357951</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003861499677799962</v>
+        <v>0.003873779058901661</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7255250259233748</v>
+        <v>0.7239647938965315</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4020420114735872</v>
+        <v>0.4033216057290656</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0005626587013781927</v>
+        <v>-0.0005638177127383182</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01165145015962987</v>
+        <v>0.01171297054447645</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02163519416902104</v>
+        <v>0.02174501406226825</v>
       </c>
     </row>
     <row r="7">
@@ -795,31 +795,31 @@
         <v>1442</v>
       </c>
       <c r="H7" t="n">
-        <v>11.06435930000043</v>
+        <v>6.856891300005373</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3961349000001064</v>
+        <v>0.3540999999968335</v>
       </c>
       <c r="J7" t="n">
-        <v>0.005344275025179557</v>
+        <v>0.005339923251920675</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004055891285625747</v>
+        <v>0.004054071124795026</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6119796688319481</v>
+        <v>0.612611331311984</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4112798831527005</v>
+        <v>0.4110992260581688</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001362877281380429</v>
+        <v>0.0001383655670857249</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01134950841977139</v>
+        <v>0.01129162032141599</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01771026043736301</v>
+        <v>0.0180601855457051</v>
       </c>
     </row>
     <row r="8">
@@ -847,10 +847,10 @@
         <v>460</v>
       </c>
       <c r="H8" t="n">
-        <v>2.50770890000058</v>
+        <v>1.927923200011719</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02918359999966924</v>
+        <v>0.01895609998609871</v>
       </c>
       <c r="J8" t="n">
         <v>0.003361956522364541</v>
@@ -899,31 +899,31 @@
         <v>751</v>
       </c>
       <c r="H9" t="n">
-        <v>5.459630999999717</v>
+        <v>3.811245599994436</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6023948999991262</v>
+        <v>0.3993240999989212</v>
       </c>
       <c r="J9" t="n">
-        <v>0.005277975989121441</v>
+        <v>0.005264684758805715</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003857655524988205</v>
+        <v>0.003847518677626944</v>
       </c>
       <c r="L9" t="n">
-        <v>0.74239809198379</v>
+        <v>0.7436938672038425</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4019886313644418</v>
+        <v>0.4009339613307528</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0001844160227261029</v>
+        <v>-0.0001834026553945332</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01119487771609451</v>
+        <v>0.01141735136280259</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01955722899767021</v>
+        <v>0.01938954504159762</v>
       </c>
     </row>
     <row r="10">
@@ -951,31 +951,31 @@
         <v>1442</v>
       </c>
       <c r="H10" t="n">
-        <v>9.887832399999752</v>
+        <v>7.430133499961812</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4077044000005117</v>
+        <v>0.4667083999956958</v>
       </c>
       <c r="J10" t="n">
-        <v>0.00545957633238237</v>
+        <v>0.00545727640757189</v>
       </c>
       <c r="K10" t="n">
-        <v>0.004165840177227336</v>
+        <v>0.004168273114401232</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5935344062991537</v>
+        <v>0.5938767930849467</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4221121143105409</v>
+        <v>0.4223434242404832</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0001438800355510886</v>
+        <v>-0.000152092646010476</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01104847486041976</v>
+        <v>0.01101141859288821</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01982624259942922</v>
+        <v>0.01948226484154392</v>
       </c>
     </row>
     <row r="11">
@@ -1003,10 +1003,10 @@
         <v>460</v>
       </c>
       <c r="H11" t="n">
-        <v>2.534063399998558</v>
+        <v>2.11243670003023</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03757919999952719</v>
+        <v>0.02019939996534958</v>
       </c>
       <c r="J11" t="n">
         <v>0.003875272004027431</v>
@@ -1055,31 +1055,31 @@
         <v>752</v>
       </c>
       <c r="H12" t="n">
-        <v>6.405069099999309</v>
+        <v>4.311280800029635</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4726971999989473</v>
+        <v>0.4460956999682821</v>
       </c>
       <c r="J12" t="n">
-        <v>0.00541739284008537</v>
+        <v>0.005408916525170895</v>
       </c>
       <c r="K12" t="n">
-        <v>0.003912939893734085</v>
+        <v>0.003898956226771551</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7286141658205898</v>
+        <v>0.729462748244214</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4078109387624964</v>
+        <v>0.4063610392962049</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0001791262596039412</v>
+        <v>-0.0001586031684427093</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0119149961806102</v>
+        <v>0.01179832115608529</v>
       </c>
       <c r="P12" t="n">
-        <v>0.02011375792294579</v>
+        <v>0.02019929855173008</v>
       </c>
     </row>
     <row r="13">
@@ -1107,31 +1107,31 @@
         <v>1442</v>
       </c>
       <c r="H13" t="n">
-        <v>12.25192869999955</v>
+        <v>7.874491800030228</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6334568999991461</v>
+        <v>0.4034592999960296</v>
       </c>
       <c r="J13" t="n">
-        <v>0.00537305014808753</v>
+        <v>0.005380859377284528</v>
       </c>
       <c r="K13" t="n">
-        <v>0.004112681274013424</v>
+        <v>0.004114208816076547</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6009942037419853</v>
+        <v>0.5998335251762958</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4170082111103836</v>
+        <v>0.4171599136752217</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0001042406616899048</v>
+        <v>9.939378844270526e-05</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01084342585767069</v>
+        <v>0.01092326868408597</v>
       </c>
       <c r="P13" t="n">
-        <v>0.02248212219508772</v>
+        <v>0.02236781170455482</v>
       </c>
     </row>
     <row r="14">
@@ -1159,10 +1159,10 @@
         <v>460</v>
       </c>
       <c r="H14" t="n">
-        <v>2.817066999999952</v>
+        <v>2.393942199996673</v>
       </c>
       <c r="I14" t="n">
-        <v>0.03371569999944768</v>
+        <v>0.02237119997153059</v>
       </c>
       <c r="J14" t="n">
         <v>0.003784037648165995</v>
@@ -1211,31 +1211,31 @@
         <v>752</v>
       </c>
       <c r="H15" t="n">
-        <v>6.115036700000928</v>
+        <v>4.170273300027475</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4861526999993657</v>
+        <v>0.5224410000373609</v>
       </c>
       <c r="J15" t="n">
-        <v>0.005917599345013172</v>
+        <v>0.005923535749195797</v>
       </c>
       <c r="K15" t="n">
-        <v>0.004212567840064515</v>
+        <v>0.004223676458437951</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6781649797886719</v>
+        <v>0.6775189404218019</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4389647319361215</v>
+        <v>0.4401304007894163</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0002669699482946951</v>
+        <v>-0.0002568003567207188</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01230914506165662</v>
+        <v>0.01234359684567462</v>
       </c>
       <c r="P15" t="n">
-        <v>0.02440087566267612</v>
+        <v>0.02482312583715418</v>
       </c>
     </row>
     <row r="16">
@@ -1263,31 +1263,31 @@
         <v>1442</v>
       </c>
       <c r="H16" t="n">
-        <v>11.49997000000076</v>
+        <v>7.83891470002709</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4223724000003131</v>
+        <v>0.4158640999812633</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00546166073155024</v>
+        <v>0.005447668008450195</v>
       </c>
       <c r="K16" t="n">
-        <v>0.004139784533540427</v>
+        <v>0.004130695161852511</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5827972943794272</v>
+        <v>0.5849322947122031</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4197417182319124</v>
+        <v>0.4188170783208486</v>
       </c>
       <c r="N16" t="n">
-        <v>2.773361654917506e-05</v>
+        <v>2.750519296642711e-05</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01136376851304301</v>
+        <v>0.01148976766762572</v>
       </c>
       <c r="P16" t="n">
-        <v>0.02144336396623592</v>
+        <v>0.02189517800340324</v>
       </c>
     </row>
   </sheetData>
